--- a/artfynd/A 63252-2023 artfynd.xlsx
+++ b/artfynd/A 63252-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63252-2023 artfynd.xlsx
+++ b/artfynd/A 63252-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1364,119 +1364,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112851778</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78021</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ljusdal, Hls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>531666</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6852196</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Lars Söderlund</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Lars Söderlund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63252-2023 artfynd.xlsx
+++ b/artfynd/A 63252-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104077309</v>
+        <v>104077252</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531666.4464660551</v>
+        <v>531621</v>
       </c>
       <c r="R2" t="n">
-        <v>6852196.293832999</v>
+        <v>6852193</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,61 +780,47 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104077252</v>
+        <v>112342453</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531621.4844896253</v>
+        <v>531667</v>
       </c>
       <c r="R3" t="n">
-        <v>6852193.041351571</v>
+        <v>6852197</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +888,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -917,12 +903,7 @@
         <v>112342436</v>
       </c>
       <c r="B4" t="n">
-        <v>89614</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531666</v>
+        <v>531667</v>
       </c>
       <c r="R4" t="n">
-        <v>6852196</v>
+        <v>6852197</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,12 +996,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1030,12 +1011,7 @@
         <v>112342444</v>
       </c>
       <c r="B5" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531666</v>
+        <v>531667</v>
       </c>
       <c r="R5" t="n">
-        <v>6852196</v>
+        <v>6852197</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,52 +1104,51 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112342453</v>
+        <v>104077309</v>
       </c>
       <c r="B6" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531666</v>
+        <v>531667</v>
       </c>
       <c r="R6" t="n">
-        <v>6852196</v>
+        <v>6852197</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,22 +1186,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,12 +1216,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1256,12 +1231,7 @@
         <v>112851208</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531666</v>
+        <v>531667</v>
       </c>
       <c r="R7" t="n">
-        <v>6852196</v>
+        <v>6852197</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1354,12 +1324,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Söderlund</t>
+          <t>Lars Söderström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 63252-2023 artfynd.xlsx
+++ b/artfynd/A 63252-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104077252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112342453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112342436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112342444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104077309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,8 +1363,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112851208</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>